--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
